--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_85_R9.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_85_R9.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6206</v>
+        <v>5.0133</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4968</v>
+        <v>4.9567</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1238</v>
+        <v>0.0566</v>
       </c>
       <c r="G2" t="n">
         <v>1.8973</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3469</v>
+        <v>1.7396</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6686</v>
+        <v>1.1286</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6783</v>
+        <v>0.6111</v>
       </c>
       <c r="V2" t="n">
         <v>1.6083</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4744</v>
+        <v>3.5545</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6413</v>
+        <v>1.8637</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1668</v>
+        <v>1.6907</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1693</v>
+        <v>0.3488</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4167</v>
+        <v>1.54</v>
       </c>
       <c r="I3" t="n">
-        <v>1.586</v>
+        <v>-1.1912</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9845</v>
+        <v>-0.0227</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6582</v>
+        <v>1.6371</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6428</v>
+        <v>-1.6597</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8152</v>
+        <v>0.3715</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7584</v>
+        <v>-0.097</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0568</v>
+        <v>0.4685</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>4.7537</v>
+        <v>1.0253</v>
       </c>
       <c r="T3" t="n">
-        <v>3.6567</v>
+        <v>0.8142</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0969</v>
+        <v>0.2111</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.1444</v>
+        <v>0.7886</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1444</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.019</v>
+        <v>3.5508</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8323</v>
+        <v>2.5919</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1866</v>
+        <v>0.9589</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3488</v>
+        <v>0.8176</v>
       </c>
       <c r="H4" t="n">
-        <v>1.54</v>
+        <v>0.6303</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1912</v>
+        <v>0.1873</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0227</v>
+        <v>1.1893</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6371</v>
+        <v>0.3697</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.6597</v>
+        <v>0.8196</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3715</v>
+        <v>-0.3717</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.097</v>
+        <v>0.2606</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4685</v>
+        <v>-0.6323</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4898</v>
+        <v>0.7332</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.3304</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.293</v>
+        <v>0.4028</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
         <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9018</v>
+        <v>3.4414</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4448</v>
+        <v>2.4753</v>
       </c>
       <c r="F5" t="n">
-        <v>1.457</v>
+        <v>0.9661</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7434</v>
+        <v>1.6504</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8031</v>
+        <v>-0.3805</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9402</v>
+        <v>2.0309</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2005</v>
+        <v>1.2864</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5749</v>
+        <v>0.3564</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6257</v>
+        <v>0.93</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.364</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2283</v>
+        <v>-0.7369</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3145</v>
+        <v>1.1009</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>3.228</v>
+        <v>1.3091</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5637</v>
+        <v>0.6528</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6642</v>
+        <v>0.6563</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6778999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8624</v>
+        <v>1.561</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9707</v>
+        <v>0.104</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8917</v>
+        <v>1.457</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8176</v>
+        <v>1.7434</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6303</v>
+        <v>0.8031</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1873</v>
+        <v>0.9402</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1893</v>
+        <v>1.2005</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3697</v>
+        <v>0.5749</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8196</v>
+        <v>0.6257</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3717</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2606</v>
+        <v>0.2283</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6323</v>
+        <v>0.3145</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0448</v>
+        <v>1.8872</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2908</v>
+        <v>1.223</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3356</v>
+        <v>0.6642</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4082</v>
+        <v>1.5446</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3077</v>
+        <v>2.9467</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1005</v>
+        <v>-1.4021</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6504</v>
+        <v>0.1693</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3805</v>
+        <v>-1.4167</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0309</v>
+        <v>1.586</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2864</v>
+        <v>0.9845</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3564</v>
+        <v>-0.6582</v>
       </c>
       <c r="L7" t="n">
-        <v>0.93</v>
+        <v>1.6428</v>
       </c>
       <c r="M7" t="n">
-        <v>0.364</v>
+        <v>-0.8152</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7369</v>
+        <v>-0.7584</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1009</v>
+        <v>-0.0568</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2759</v>
+        <v>2.8238</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5149</v>
+        <v>1.9621</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7907</v>
+        <v>0.8617</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-2.1444</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.214</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6113</v>
+        <v>0.6449</v>
       </c>
       <c r="E8" t="n">
         <v>0.5889</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="G8" t="n">
         <v>0.5889</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BACOT JR.</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1365</v>
+        <v>0.4711</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1763</v>
+        <v>-0.2073</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3129</v>
+        <v>0.6784</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4895</v>
+        <v>0.3</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8643</v>
+        <v>0.6614</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3748</v>
+        <v>-0.3614</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7469</v>
+        <v>0.8538</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9677</v>
+        <v>0.1078</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2208</v>
+        <v>0.746</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2574</v>
+        <v>-0.5538</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1034</v>
+        <v>0.5536</v>
       </c>
       <c r="O9" t="n">
-        <v>0.154</v>
+        <v>-1.1074</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1647</v>
+        <v>0.1711</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4288</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.264</v>
+        <v>0.0725</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2605</v>
+        <v>0.438</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8717</v>
+        <v>-1.4777</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6112</v>
+        <v>1.9158</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3</v>
+        <v>-0.2451</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6614</v>
+        <v>-1.7106</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3614</v>
+        <v>1.4655</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8538</v>
+        <v>-0.2593</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1078</v>
+        <v>-1.9389</v>
       </c>
       <c r="L10" t="n">
-        <v>0.746</v>
+        <v>1.6796</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5538</v>
+        <v>0.0142</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5536</v>
+        <v>0.2283</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1074</v>
+        <v>-0.214</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5605</v>
+        <v>0.2192</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5658</v>
+        <v>-0.0587</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0053</v>
+        <v>0.2779</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. BITIM</t>
+          <t>A. BACOT JR.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2804</v>
+        <v>-0.0508</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0536</v>
+        <v>-0.2629</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.334</v>
+        <v>0.212</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3252</v>
+        <v>-0.4895</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1512</v>
+        <v>-0.8643</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.174</v>
+        <v>0.3748</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0536</v>
+        <v>-0.7469</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0168</v>
+        <v>-0.9677</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0368</v>
+        <v>0.2208</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3788</v>
+        <v>0.2574</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.168</v>
+        <v>0.1034</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2108</v>
+        <v>0.154</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0448</v>
+        <v>-0.0226</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.3422</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0448</v>
+        <v>-0.3648</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>O. BITIM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4168</v>
+        <v>-0.2132</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3662</v>
+        <v>0.0536</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9494</v>
+        <v>-0.2668</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2451</v>
+        <v>-0.3252</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7106</v>
+        <v>-0.1512</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4655</v>
+        <v>-0.174</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2593</v>
+        <v>0.0536</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9389</v>
+        <v>0.0168</v>
       </c>
       <c r="L12" t="n">
-        <v>1.6796</v>
+        <v>0.0368</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0142</v>
+        <v>-0.3788</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2283</v>
+        <v>-0.168</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.214</v>
+        <v>-0.2108</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6357</v>
+        <v>0.112</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9471000000000001</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3115</v>
+        <v>0.112</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7151</v>
+        <v>-4.1007</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.5242</v>
+        <v>-4.7418</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8091</v>
+        <v>0.6411</v>
       </c>
       <c r="G13" t="n">
         <v>-4.278</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8984</v>
+        <v>-0.284</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.963</v>
+        <v>-0.1806</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0646</v>
+        <v>-0.1034</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9304</v>
@@ -1501,25 +1501,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.3614</v>
+        <v>15.8549</v>
       </c>
       <c r="E14" t="n">
-        <v>7.3977</v>
+        <v>8.891099999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>6.9638</v>
+        <v>6.963699999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>2.177900000000001</v>
+        <v>2.177900000000002</v>
       </c>
       <c r="H14" t="n">
         <v>-6.236899999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>8.414799999999998</v>
+        <v>8.4148</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1269</v>
+        <v>3.126899999999999</v>
       </c>
       <c r="K14" t="n">
         <v>-5.3204</v>
@@ -1528,10 +1528,10 @@
         <v>8.4476</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9490000000000003</v>
+        <v>-0.9489999999999998</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9163000000000001</v>
+        <v>-0.9162999999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-0.03269999999999973</v>
@@ -1546,13 +1546,13 @@
         <v>11.5977</v>
       </c>
       <c r="S14" t="n">
-        <v>8.276400000000001</v>
+        <v>9.7699</v>
       </c>
       <c r="T14" t="n">
-        <v>4.818999999999999</v>
+        <v>6.3126</v>
       </c>
       <c r="U14" t="n">
-        <v>3.4573</v>
+        <v>3.4574</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8919</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8619</v>
+        <v>3.2221</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1412</v>
+        <v>5.1976</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2793</v>
+        <v>-1.9755</v>
       </c>
       <c r="G15" t="n">
         <v>3.6134</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1278</v>
+        <v>-0.7677</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6097</v>
+        <v>-0.3339</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7376</v>
+        <v>-0.4338</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9659</v>
+        <v>1.51</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4587</v>
+        <v>-0.8126</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4246</v>
+        <v>2.3226</v>
       </c>
       <c r="G16" t="n">
         <v>2.7841</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6764</v>
+        <v>-1.1323</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3927</v>
+        <v>-0.7466</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2836</v>
+        <v>-0.3857</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1418</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2757</v>
+        <v>1.1242</v>
       </c>
       <c r="E17" t="n">
-        <v>0.549</v>
+        <v>0.9029</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2733</v>
+        <v>0.2213</v>
       </c>
       <c r="G17" t="n">
         <v>1.4924</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.057</v>
+        <v>-0.2084</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1845</v>
+        <v>0.3102</v>
       </c>
       <c r="V17" t="n">
         <v>0.5361</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0355</v>
+        <v>-1.7603</v>
       </c>
       <c r="E18" t="n">
-        <v>0.252</v>
+        <v>-0.1018</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2876</v>
+        <v>-1.6585</v>
       </c>
       <c r="G18" t="n">
         <v>0.9258999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3145</v>
+        <v>-0.0393</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1608</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1537</v>
+        <v>0.4753</v>
       </c>
       <c r="V18" t="n">
         <v>-1.719</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7337</v>
+        <v>-2.2733</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1345</v>
+        <v>-0.8986</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5992</v>
+        <v>-1.3747</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2938</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2801</v>
+        <v>-0.8197</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.608</v>
+        <v>-0.3835</v>
       </c>
       <c r="V19" t="n">
         <v>0.5361</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4583</v>
+        <v>-2.4919</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.3882</v>
+        <v>-3.9164</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9298999999999999</v>
+        <v>1.4245</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1511</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1474</v>
+        <v>-0.181</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.731</v>
+        <v>-0.2592</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4164</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5361</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3135</v>
+        <v>-3.6115</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.0861</v>
+        <v>-4.7323</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7726</v>
+        <v>1.1208</v>
       </c>
       <c r="G21" t="n">
         <v>-6.2918</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0038</v>
+        <v>-0.3018</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6484</v>
+        <v>-0.2946</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3554</v>
+        <v>-0.0072</v>
       </c>
       <c r="V21" t="n">
         <v>2.2862</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.9238</v>
+        <v>-6.1488</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9106</v>
+        <v>-3.6747</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0131</v>
+        <v>-2.4741</v>
       </c>
       <c r="G22" t="n">
         <v>-3.257</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6693</v>
+        <v>-0.8944</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5895</v>
+        <v>-0.3536</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0798</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-14.3613</v>
+        <v>-10.4295</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.035900000000002</v>
+        <v>-8.035899999999998</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.325399999999999</v>
+        <v>-2.3936</v>
       </c>
       <c r="G23" t="n">
         <v>-2.177900000000001</v>
@@ -2248,13 +2248,13 @@
         <v>5.798999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.276299999999999</v>
+        <v>-4.3446</v>
       </c>
       <c r="T23" t="n">
         <v>-3.4573</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.819000000000001</v>
+        <v>-0.8873</v>
       </c>
       <c r="V23" t="n">
         <v>1.8919</v>
